--- a/data/trans_orig/P64D1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64D1_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>53515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>41945</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34136</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52604</t>
+          <t>50096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>79757</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50623</t>
+          <t>64917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79498</t>
+          <t>96946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>111190</t>
+          <t>126123</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100300</t>
+          <t>110420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119149</t>
+          <t>138473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37997</t>
+          <t>46051</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27843</t>
+          <t>37900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46311</t>
+          <t>54185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>149187</t>
+          <t>172173</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133052</t>
+          <t>154984</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161927</t>
+          <t>187013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80447</t>
+          <t>87996</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80447</t>
+          <t>87996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80447</t>
+          <t>87996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>251930</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>251930</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>251930</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>303712</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138611</t>
+          <t>269283</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>330864</t>
+          <t>340639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>385312</t>
+          <t>362855</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>323974</t>
+          <t>335155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>516549</t>
+          <t>386987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>648381</t>
+          <t>666567</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>468646</t>
+          <t>621828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>801297</t>
+          <t>713333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1119314</t>
+          <t>966803</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1051519</t>
+          <t>929876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1243772</t>
+          <t>1001232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>559651</t>
+          <t>582417</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428414</t>
+          <t>558285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>620989</t>
+          <t>610117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1678965</t>
+          <t>1549220</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1526049</t>
+          <t>1502454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1858700</t>
+          <t>1593959</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1382383</t>
+          <t>1270515</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1382383</t>
+          <t>1270515</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1382383</t>
+          <t>1270515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>944963</t>
+          <t>945272</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>944963</t>
+          <t>945272</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>944963</t>
+          <t>945272</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2327346</t>
+          <t>2215787</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2327346</t>
+          <t>2215787</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2327346</t>
+          <t>2215787</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>122748</t>
+          <t>134296</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102796</t>
+          <t>114950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144515</t>
+          <t>155742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>148495</t>
+          <t>165766</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133745</t>
+          <t>149037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167193</t>
+          <t>185008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>271243</t>
+          <t>300063</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247356</t>
+          <t>273777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>298503</t>
+          <t>331088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>324532</t>
+          <t>353275</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302765</t>
+          <t>331829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>344484</t>
+          <t>372621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>286864</t>
+          <t>311710</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>268166</t>
+          <t>292468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>301614</t>
+          <t>328439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>611396</t>
+          <t>664985</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584136</t>
+          <t>633960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635283</t>
+          <t>691271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>447280</t>
+          <t>487571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>447280</t>
+          <t>487571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>447280</t>
+          <t>487571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>435359</t>
+          <t>477476</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>435359</t>
+          <t>477476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>435359</t>
+          <t>477476</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>882639</t>
+          <t>965048</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>882639</t>
+          <t>965048</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>882639</t>
+          <t>965048</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>406730</t>
+          <t>475820</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>265480</t>
+          <t>435580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>476367</t>
+          <t>523814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>576256</t>
+          <t>570567</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>517723</t>
+          <t>537425</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>711668</t>
+          <t>604874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>982987</t>
+          <t>1046387</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>789432</t>
+          <t>993988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1136263</t>
+          <t>1101438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1555036</t>
+          <t>1446202</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1485399</t>
+          <t>1398208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1696286</t>
+          <t>1486442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>884513</t>
+          <t>940177</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>749101</t>
+          <t>905870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>943046</t>
+          <t>973319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2439548</t>
+          <t>2386378</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2286272</t>
+          <t>2331327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2633103</t>
+          <t>2438777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1961766</t>
+          <t>1922022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1961766</t>
+          <t>1922022</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1961766</t>
+          <t>1922022</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1460769</t>
+          <t>1510744</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1460769</t>
+          <t>1510744</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1460769</t>
+          <t>1510744</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3422535</t>
+          <t>3432765</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3422535</t>
+          <t>3432765</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3422535</t>
+          <t>3432765</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
